--- a/椙山改修/261030_課題リスト（1023_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1023_分科会後）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="課題リスト" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="運用ルール" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="課題リスト" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用ルール" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'課題リスト'!$A$1:$P$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'課題リスト'!$A$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>　</t>
+          <t xml:space="preserve">　</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t>　</t>
+          <t xml:space="preserve">　</t>
         </is>
       </c>
       <c r="H5" s="131" t="n">
@@ -3557,7 +3557,7 @@
       <c r="O43" s="155" t="n"/>
       <c r="P43" s="43" t="n"/>
     </row>
-    <row r="44" ht="49" customFormat="1" customHeight="1" s="98">
+    <row r="44" ht="88" customFormat="1" customHeight="1" s="98">
       <c r="A44" s="46" t="n">
         <v>39</v>
       </c>
@@ -3599,7 +3599,10 @@
         <is>
           <t>・10/23 第6回分科会　ルーバー部の点検口は4か所（位置は要確認）
 ・プルボックス上は取外し式ルーバー1本で点検対応する方向
-・天井との取合いはクリアランス20mmで確認（要確認）</t>
+・天井との取合いはクリアランス20mmで確認（要確認）
+・10/30 第7回分科会　ルーバー内の照明は端から1本手前で始めて終える案（直線で納める）
+・吸音ルーバー内にルーバーと同方向のライティングレールを設ける案を検討
+・ルーバー固定のZ金物は端部から約100〜150mm、中間は約450mmピッチを目安</t>
         </is>
       </c>
       <c r="M44" s="154" t="n"/>
@@ -3655,7 +3658,7 @@
       <c r="O45" s="155" t="n"/>
       <c r="P45" s="43" t="n"/>
     </row>
-    <row r="46" ht="75" customFormat="1" customHeight="1" s="98">
+    <row r="46" ht="114" customFormat="1" customHeight="1" s="98">
       <c r="A46" s="46" t="n">
         <v>41</v>
       </c>
@@ -3703,7 +3706,10 @@
         <is>
           <t>・10/23 第6回分科会　AD：エンジンの配線がランマ上から見える→ランマ中央に新設して隠す（要確認）
 ・ハンガードア：床レールは飛び出さないタイプで作図。上部吊金具の耐荷重に懸念あり（要確認）
-・SD点検口は塗装とする</t>
+・SD点検口は塗装とする
+・10/30 第7回分科会　ハンガードア：扉本体約180kg（パネル貼りで約200kg）。指挟み・寄りかかり時の安全に配慮
+・隙間は極力小さくする方向。壁とのクリアランスは30→20mmに変更する案で検討
+・ローラー・三方枠が目立たない納まりで修正図を作成。戸当り・ストッパー仕様と隙間寸法は安全性を含めて継続確認</t>
         </is>
       </c>
       <c r="M46" s="154" t="n"/>
@@ -3713,123 +3719,326 @@
       <c r="O46" s="155" t="n"/>
       <c r="P46" s="43" t="n"/>
     </row>
-    <row r="47" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A47" s="15" t="n"/>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="149" t="n"/>
-      <c r="I47" s="24" t="n"/>
-      <c r="J47" s="18" t="n"/>
-      <c r="K47" s="17" t="n"/>
-      <c r="L47" s="25" t="n"/>
-      <c r="M47" s="153" t="n"/>
-      <c r="N47" s="149" t="n"/>
-      <c r="O47" s="19" t="n"/>
-      <c r="P47" s="20" t="n"/>
+    <row r="47" ht="75" customFormat="1" customHeight="1" s="98">
+      <c r="A47" s="46" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C47" s="47" t="n"/>
+      <c r="D47" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E47" s="47" t="n"/>
+      <c r="F47" s="47" t="n"/>
+      <c r="G47" s="47" t="n"/>
+      <c r="H47" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I47" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J47" s="49" t="inlineStr">
+        <is>
+          <t>天井照明
+・厨房開口上のボックス
+・西側間接照明
+・ダウンライト計画</t>
+        </is>
+      </c>
+      <c r="K47" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L47" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　厨房側は照明ボックスを設けず、吊り具を使う器具を検討。ルーバーとの干渉、点検・感知器の位置を確認
+・西側間接照明は器具とアルミ見切り材・レールの干渉を確認。器具の向き・必要寸法を踏まえて納まりを検討
+・ダウンライトは3500K、φ75・100・125を含め、ランダムに見える配置で調整</t>
+        </is>
+      </c>
+      <c r="M47" s="154" t="n"/>
+      <c r="N47" s="151" t="n"/>
+      <c r="O47" s="155" t="n"/>
+      <c r="P47" s="43" t="n"/>
     </row>
     <row r="48" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A48" s="15" t="n"/>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="149" t="n"/>
-      <c r="I48" s="24" t="n"/>
-      <c r="J48" s="18" t="n"/>
-      <c r="K48" s="17" t="n"/>
-      <c r="L48" s="25" t="n"/>
-      <c r="M48" s="153" t="n"/>
-      <c r="N48" s="149" t="n"/>
-      <c r="O48" s="19" t="n"/>
-      <c r="P48" s="20" t="n"/>
-    </row>
-    <row r="49" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A49" s="15" t="n"/>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="149" t="n"/>
-      <c r="I49" s="24" t="n"/>
-      <c r="J49" s="18" t="n"/>
-      <c r="K49" s="17" t="n"/>
-      <c r="L49" s="25" t="n"/>
-      <c r="M49" s="153" t="n"/>
-      <c r="N49" s="149" t="n"/>
-      <c r="O49" s="19" t="n"/>
-      <c r="P49" s="20" t="n"/>
-    </row>
-    <row r="50" ht="128.25" customFormat="1" customHeight="1" s="98">
-      <c r="A50" s="14" t="n"/>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="21" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
-      <c r="H50" s="124" t="n"/>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="22" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="M50" s="125" t="n"/>
-      <c r="N50" s="14" t="n"/>
-      <c r="O50" s="23" t="n"/>
-    </row>
-    <row r="51" ht="50.1" customFormat="1" customHeight="1" s="98">
-      <c r="A51" s="14" t="n"/>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="124" t="n"/>
-      <c r="I51" s="14" t="n"/>
-      <c r="J51" s="22" t="n"/>
-      <c r="K51" s="14" t="n"/>
-      <c r="M51" s="125" t="n"/>
-      <c r="N51" s="14" t="n"/>
-      <c r="O51" s="23" t="n"/>
-    </row>
-    <row r="52" ht="107.7" customFormat="1" customHeight="1" s="98">
-      <c r="A52" s="14" t="n"/>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="124" t="n"/>
-      <c r="I52" s="14" t="n"/>
-      <c r="J52" s="22" t="n"/>
-      <c r="K52" s="14" t="n"/>
-      <c r="M52" s="125" t="n"/>
-      <c r="N52" s="14" t="n"/>
-      <c r="O52" s="23" t="n"/>
-    </row>
-    <row r="53" ht="50.1" customFormat="1" customHeight="1" s="98">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="21" t="n"/>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
-      <c r="H53" s="124" t="n"/>
-      <c r="I53" s="14" t="n"/>
-      <c r="J53" s="22" t="n"/>
-      <c r="K53" s="14" t="n"/>
-      <c r="M53" s="125" t="n"/>
-      <c r="N53" s="14" t="n"/>
-      <c r="O53" s="23" t="n"/>
+      <c r="A48" s="46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C48" s="47" t="n"/>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="n"/>
+      <c r="F48" s="47" t="n"/>
+      <c r="G48" s="47" t="n"/>
+      <c r="H48" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I48" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J48" s="49" t="inlineStr">
+        <is>
+          <t>1階平面詳細図：家具配置とコンセント位置</t>
+        </is>
+      </c>
+      <c r="K48" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L48" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　椅子・カウンター等の家具配置を確認し、配置変更に伴う家具用コンセント位置への影響を整理する</t>
+        </is>
+      </c>
+      <c r="M48" s="154" t="n"/>
+      <c r="N48" s="151" t="n"/>
+      <c r="O48" s="155" t="n"/>
+      <c r="P48" s="43" t="n"/>
+    </row>
+    <row r="49" ht="49" customFormat="1" customHeight="1" s="98">
+      <c r="A49" s="46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C49" s="47" t="n"/>
+      <c r="D49" s="47" t="n"/>
+      <c r="E49" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F49" s="47" t="n"/>
+      <c r="G49" s="47" t="n"/>
+      <c r="H49" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I49" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J49" s="49" t="inlineStr">
+        <is>
+          <t>東側デッキ床下のPAC・RA・SAの納まり</t>
+        </is>
+      </c>
+      <c r="K49" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L49" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　床下空調の吸込口として、階段付近の段差にガラリを設けダクトを接続する案を検討
+・ガラリ・ダクトと家具・コンセントの干渉を確認</t>
+        </is>
+      </c>
+      <c r="M49" s="154" t="n"/>
+      <c r="N49" s="151" t="n"/>
+      <c r="O49" s="155" t="n"/>
+      <c r="P49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="75" customFormat="1" customHeight="1" s="98">
+      <c r="A50" s="48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C50" s="47" t="n"/>
+      <c r="D50" s="47" t="n"/>
+      <c r="E50" s="47" t="n"/>
+      <c r="F50" s="47" t="n"/>
+      <c r="G50" s="47" t="n"/>
+      <c r="H50" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I50" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J50" s="49" t="inlineStr">
+        <is>
+          <t>モルタルアートの範囲・仕上げ色</t>
+        </is>
+      </c>
+      <c r="K50" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L50" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　仕上げは図面の色分けに沿って青系・グレー系を使い分ける方向
+・入口付近は木の壁の小口までを木仕上げ、内側側面をモルタル仕上げとする案を確認
+・天井はN3、壁はEP仕上げを想定。モルタルアートに近い色・サッシの塗装色は色見本で確認</t>
+        </is>
+      </c>
+      <c r="M50" s="154" t="n"/>
+      <c r="N50" s="151" t="n"/>
+      <c r="O50" s="155" t="n"/>
+      <c r="P50" s="43" t="n"/>
+    </row>
+    <row r="51" ht="40.05" customFormat="1" customHeight="1" s="98">
+      <c r="A51" s="48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C51" s="47" t="n"/>
+      <c r="D51" s="47" t="n"/>
+      <c r="E51" s="47" t="n"/>
+      <c r="F51" s="47" t="n"/>
+      <c r="G51" s="47" t="n"/>
+      <c r="H51" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I51" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J51" s="49" t="inlineStr">
+        <is>
+          <t>タイル割付図（打）の確認・修正</t>
+        </is>
+      </c>
+      <c r="K51" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L51" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　東側タイルの割付、階段寸法、腰壁タイルのモール・目地仕様を図面で確認・修正する</t>
+        </is>
+      </c>
+      <c r="M51" s="154" t="n"/>
+      <c r="N51" s="151" t="n"/>
+      <c r="O51" s="155" t="n"/>
+      <c r="P51" s="43" t="n"/>
+    </row>
+    <row r="52" ht="49" customFormat="1" customHeight="1" s="98">
+      <c r="A52" s="48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C52" s="47" t="n"/>
+      <c r="D52" s="47" t="n"/>
+      <c r="E52" s="47" t="n"/>
+      <c r="F52" s="47" t="n"/>
+      <c r="G52" s="47" t="n"/>
+      <c r="H52" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I52" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J52" s="49" t="inlineStr">
+        <is>
+          <t>解体範囲の確認</t>
+        </is>
+      </c>
+      <c r="K52" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L52" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　床レベル調整に伴うタイル撤去・下地調整の範囲を確認
+・既存設備・壁（ボックス含む）の残置範囲を確認
+・撤去後の穴・開口部の補修方法を確認</t>
+        </is>
+      </c>
+      <c r="M52" s="154" t="n"/>
+      <c r="N52" s="151" t="n"/>
+      <c r="O52" s="155" t="n"/>
+      <c r="P52" s="43" t="n"/>
+    </row>
+    <row r="53" ht="62" customFormat="1" customHeight="1" s="98">
+      <c r="A53" s="48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="47" t="n"/>
+      <c r="C53" s="47" t="n"/>
+      <c r="D53" s="47" t="n"/>
+      <c r="E53" s="47" t="n"/>
+      <c r="F53" s="47" t="n"/>
+      <c r="G53" s="47" t="n"/>
+      <c r="H53" s="151" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I53" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J53" s="49" t="inlineStr">
+        <is>
+          <t>既存設備（オペレーター）の対応</t>
+        </is>
+      </c>
+      <c r="K53" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SC</t>
+        </is>
+      </c>
+      <c r="L53" s="50" t="inlineStr">
+        <is>
+          <t>・10/30 第7回分科会　現状復旧は難しい可能性があるため、復旧費用や複数箇所に分けて動作させる案を関係者に説明する
+・不使用の場合の撤去案と、撤去後の下部設備の移設案も併せて共有
+・費用の内訳・金額は別途確認</t>
+        </is>
+      </c>
+      <c r="M53" s="154" t="n"/>
+      <c r="N53" s="151" t="n"/>
+      <c r="O53" s="155" t="n"/>
+      <c r="P53" s="43" t="n"/>
     </row>
     <row r="54" ht="114" customFormat="1" customHeight="1" s="98">
       <c r="A54" s="14" t="n"/>
@@ -4687,7 +4896,7 @@
     <mergeCell ref="O3:O4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5:G49" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5:G53" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"　,〇"</formula1>
     </dataValidation>
   </dataValidations>

--- a/椙山改修/261030_課題リスト（1023_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1023_分科会後）.xlsx
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M8" s="142" t="n"/>
       <c r="N8" s="143" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O8" s="144" t="n"/>
       <c r="P8" s="108" t="n"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="M9" s="142" t="n"/>
       <c r="N9" s="146" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O9" s="147" t="n"/>
       <c r="P9" s="114" t="n"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="M23" s="153" t="n"/>
       <c r="N23" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O23" s="152" t="n"/>
       <c r="P23" s="20" t="n"/>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="M25" s="153" t="n"/>
       <c r="N25" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O25" s="152" t="n"/>
       <c r="P25" s="20" t="n"/>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="M27" s="153" t="n"/>
       <c r="N27" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O27" s="152" t="n"/>
       <c r="P27" s="20" t="n"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="M32" s="157" t="n"/>
       <c r="N32" s="156" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O32" s="146" t="n"/>
       <c r="P32" s="123" t="n"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="M33" s="154" t="n"/>
       <c r="N33" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O33" s="155" t="n"/>
       <c r="P33" s="43" t="n"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="M36" s="157" t="n"/>
       <c r="N36" s="156" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O36" s="146" t="n"/>
       <c r="P36" s="123" t="n"/>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="M38" s="154" t="n"/>
       <c r="N38" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O38" s="155" t="n"/>
       <c r="P38" s="43" t="n"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M40" s="157" t="n"/>
       <c r="N40" s="156" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O40" s="146" t="n"/>
       <c r="P40" s="123" t="n"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M42" s="154" t="n"/>
       <c r="N42" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O42" s="155" t="n"/>
       <c r="P42" s="43" t="n"/>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M43" s="154" t="n"/>
       <c r="N43" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O43" s="155" t="n"/>
       <c r="P43" s="43" t="n"/>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="M44" s="154" t="n"/>
       <c r="N44" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O44" s="155" t="n"/>
       <c r="P44" s="43" t="n"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="M45" s="154" t="n"/>
       <c r="N45" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O45" s="155" t="n"/>
       <c r="P45" s="43" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="M46" s="154" t="n"/>
       <c r="N46" s="151" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="O46" s="155" t="n"/>
       <c r="P46" s="43" t="n"/>
@@ -3767,7 +3767,9 @@
         </is>
       </c>
       <c r="M47" s="154" t="n"/>
-      <c r="N47" s="151" t="n"/>
+      <c r="N47" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O47" s="155" t="n"/>
       <c r="P47" s="43" t="n"/>
     </row>
@@ -3814,7 +3816,9 @@
         </is>
       </c>
       <c r="M48" s="154" t="n"/>
-      <c r="N48" s="151" t="n"/>
+      <c r="N48" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O48" s="155" t="n"/>
       <c r="P48" s="43" t="n"/>
     </row>
@@ -3862,7 +3866,9 @@
         </is>
       </c>
       <c r="M49" s="154" t="n"/>
-      <c r="N49" s="151" t="n"/>
+      <c r="N49" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O49" s="155" t="n"/>
       <c r="P49" s="43" t="n"/>
     </row>
@@ -3907,7 +3913,9 @@
         </is>
       </c>
       <c r="M50" s="154" t="n"/>
-      <c r="N50" s="151" t="n"/>
+      <c r="N50" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O50" s="155" t="n"/>
       <c r="P50" s="43" t="n"/>
     </row>
@@ -3950,7 +3958,9 @@
         </is>
       </c>
       <c r="M51" s="154" t="n"/>
-      <c r="N51" s="151" t="n"/>
+      <c r="N51" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O51" s="155" t="n"/>
       <c r="P51" s="43" t="n"/>
     </row>
@@ -3995,7 +4005,9 @@
         </is>
       </c>
       <c r="M52" s="154" t="n"/>
-      <c r="N52" s="151" t="n"/>
+      <c r="N52" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O52" s="155" t="n"/>
       <c r="P52" s="43" t="n"/>
     </row>
@@ -4036,7 +4048,9 @@
         </is>
       </c>
       <c r="M53" s="154" t="n"/>
-      <c r="N53" s="151" t="n"/>
+      <c r="N53" s="151" t="n">
+        <v>46332</v>
+      </c>
       <c r="O53" s="155" t="n"/>
       <c r="P53" s="43" t="n"/>
     </row>
